--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/ILLINOIS_2019.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/ILLINOIS_2019.xlsx
@@ -2976,7 +2976,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C146">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C200">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C357">
@@ -7591,7 +7591,7 @@
         <v>63</v>
       </c>
       <c r="D402">
-        <v>0.0009114055899542851</v>
+        <v>0.0009114055899542852</v>
       </c>
     </row>
     <row r="403">
@@ -7753,7 +7753,7 @@
         <v>66</v>
       </c>
       <c r="D411">
-        <v>0.0009548058561425843</v>
+        <v>0.0009548058561425844</v>
       </c>
     </row>
     <row r="412">
@@ -11353,7 +11353,7 @@
         <v>63</v>
       </c>
       <c r="D611">
-        <v>0.0009114055899542851</v>
+        <v>0.0009114055899542852</v>
       </c>
     </row>
     <row r="612">
@@ -15277,7 +15277,7 @@
         <v>63</v>
       </c>
       <c r="D829">
-        <v>0.0009114055899542851</v>
+        <v>0.0009114055899542852</v>
       </c>
     </row>
     <row r="830">
@@ -15558,7 +15558,7 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C845">
@@ -18528,7 +18528,7 @@
       </c>
       <c r="B1010" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C1010">
@@ -19446,7 +19446,7 @@
       </c>
       <c r="B1061" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C1061">
@@ -21631,7 +21631,7 @@
         <v>66</v>
       </c>
       <c r="D1182">
-        <v>0.0009548058561425843</v>
+        <v>0.0009548058561425844</v>
       </c>
     </row>
     <row r="1183">
@@ -31963,7 +31963,7 @@
         <v>63</v>
       </c>
       <c r="D1756">
-        <v>0.0009114055899542851</v>
+        <v>0.0009114055899542852</v>
       </c>
     </row>
     <row r="1757">
